--- a/docs/Solvix-Full-Story-Backlog.xlsx
+++ b/docs/Solvix-Full-Story-Backlog.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Phase Overview" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Backlog!$A$1:$K$34</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Backlog!$A$1:$K$38</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="237">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -90,87 +90,90 @@
     <t xml:space="preserve">epic:repo-understanding, priority:must, type:feature, phase:1</t>
   </si>
   <si>
+    <t xml:space="preserve">Done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retrieve relevant files for a task</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want the agent to find the right files for a given task automatically, so that I don't have to manually point it at the relevant code.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Given a task description, the top-N retrieved files include the file(s) actually requiring changes, verified against a labeled test set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respect project conventions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want the agent to understand project conventions (style, structure, existing patterns), so that its changes fit naturally into the codebase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent-authored code passes the project's existing linter without manual fixes in the common case.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Should</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epic:repo-understanding, priority:should, type:feature, phase:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B: Requirement Understanding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accept plain-language task input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want to give the agent a plain-language description of a feature or bug, so that I don't have to write a formal spec.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free-text input is accepted; agent produces a task plan before making changes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epic:requirement-understanding, priority:must, type:feature, phase:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask clarifying questions on ambiguity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want the agent to ask clarifying questions when a requirement is ambiguous, so that it doesn't guess wrong and waste a cycle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If confidence in scope is low (e.g. multiple valid interpretations), agent surfaces a question instead of proceeding blindly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epic:requirement-understanding, priority:should, type:feature, phase:1</t>
+  </si>
+  <si>
     <t xml:space="preserve">To Do</t>
   </si>
   <si>
-    <t xml:space="preserve">SLX-A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retrieve relevant files for a task</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a developer, I want the agent to find the right files for a given task automatically, so that I don't have to manually point it at the relevant code.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Given a task description, the top-N retrieved files include the file(s) actually requiring changes, verified against a labeled test set.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLX-A3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Respect project conventions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a developer, I want the agent to understand project conventions (style, structure, existing patterns), so that its changes fit naturally into the codebase.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent-authored code passes the project's existing linter without manual fixes in the common case.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Should</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epic:repo-understanding, priority:should, type:feature, phase:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLX-B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B: Requirement Understanding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accept plain-language task input</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a developer, I want to give the agent a plain-language description of a feature or bug, so that I don't have to write a formal spec.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free-text input is accepted; agent produces a task plan before making changes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epic:requirement-understanding, priority:must, type:feature, phase:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLX-B2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint 8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ask clarifying questions on ambiguity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a developer, I want the agent to ask clarifying questions when a requirement is ambiguous, so that it doesn't guess wrong and waste a cycle.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If confidence in scope is low (e.g. multiple valid interpretations), agent surfaces a question instead of proceeding blindly.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epic:requirement-understanding, priority:should, type:feature, phase:1</t>
-  </si>
-  <si>
     <t xml:space="preserve">SLX-B3</t>
   </si>
   <si>
@@ -628,6 +631,57 @@
   </si>
   <si>
     <t xml:space="preserve">epic:dev-experience, priority:should, type:feature, phase:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-A4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incremental re-indexing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want the indexer to re-index only changed files on subsequent runs, so that repeated indexing is fast and doesn't waste time/compute re-embedding unchanged code.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On a second index_repo() call, only files whose content hash has changed since the last index are re-chunked and re-embedded; unchanged files' existing vectors/symbols are reused.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-A5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truncate context to model budget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want the assembled context (retrieved chunks, symbol matches, related files) ranked and truncated to fit the reasoning model's context window, so that large tasks don't silently overflow or get an incoherent, oversized prompt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Given a retrieval result larger than the configured token budget, the assembler ranks sources by priority (exact symbol match &gt; high-similarity chunk &gt; one-hop related file) and truncates to fit, without cutting a chunk mid-function.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-E4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reduce dangerous-ops false positives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want the dangerous-ops patterns to match actual SQL/git commands rather than bare identifier names, so that ordinary code (e.g. a variable or function named truncate) does not constantly trigger unnecessary confirmation prompts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Given a diff containing the word "truncate" (or similar) only as a plain code identifier and not as part of an actual SQL/git destructive command, check_dangerous_ops does not flag it; the existing built-in destructive-command patterns still fire correctly on real dangerous commands.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epic:safety, priority:should, type:bug, phase:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-P3-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interactive live-edit mode (solvix chat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want an interactive mode where the agent proposes one diff at a time directly against my real working files (not a sandboxed scratch copy ending in a PR), so that I can review and approve changes live, similar to working with a pair-programming assistant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Running  reads the repo the same way as , but proposes each diff directly against the real working tree one step at a time, waits for explicit per-diff approval before writing it, and does not require a full task to complete before any change is visible — this is an additive mode alongside the existing sandboxed, PR-based  flow, not a replacement for it.</t>
   </si>
   <si>
     <t xml:space="preserve">Focus</t>
@@ -835,8 +889,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1205,1213 +1263,1353 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="3" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="C10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="2" t="s">
+      <c r="E35" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="J36" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H9" s="5" t="s">
+      <c r="C37" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="H37" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" s="2" t="s">
+      <c r="I37" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" s="2" t="s">
+      <c r="J37" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="H38" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="J22" s="2" t="s">
+      <c r="I38" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="K22" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
+      <c r="J38" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B32" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>21</v>
+      <c r="K38" s="3" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K34"/>
+  <autoFilter ref="A1:K38"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2431,326 +2629,326 @@
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="C1" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D2" s="2" t="n">
+      <c r="C2" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A2)</f>
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <f aca="false">SUMIF(Backlog!D:D,A2,Backlog!I:I)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D3" s="2" t="n">
+      <c r="C3" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A3)</f>
-        <v>3</v>
-      </c>
-      <c r="E3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <f aca="false">SUMIF(Backlog!D:D,A3,Backlog!I:I)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D4" s="2" t="n">
+      <c r="C4" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A4)</f>
         <v>2</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <f aca="false">SUMIF(Backlog!D:D,A4,Backlog!I:I)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D5" s="2" t="n">
+      <c r="C5" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A5)</f>
         <v>2</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <f aca="false">SUMIF(Backlog!D:D,A5,Backlog!I:I)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" s="3" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D6" s="2" t="n">
+      <c r="C6" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A6)</f>
         <v>4</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <f aca="false">SUMIF(Backlog!D:D,A6,Backlog!I:I)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="3" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D7" s="2" t="n">
+      <c r="C7" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D7" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A7)</f>
-        <v>4</v>
-      </c>
-      <c r="E7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="3" t="n">
         <f aca="false">SUMIF(Backlog!D:D,A7,Backlog!I:I)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="3" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="C8" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D8" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A8)</f>
         <v>1</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="3" t="n">
         <f aca="false">SUMIF(Backlog!D:D,A8,Backlog!I:I)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D9" s="2" t="n">
+      <c r="C9" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D9" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A9)</f>
         <v>3</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="3" t="n">
         <f aca="false">SUMIF(Backlog!D:D,A9,Backlog!I:I)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D10" s="2" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D10" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A10)</f>
         <v>2</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="3" t="n">
         <f aca="false">SUMIF(Backlog!D:D,A10,Backlog!I:I)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D11" s="2" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D11" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A11)</f>
         <v>2</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="3" t="n">
         <f aca="false">SUMIF(Backlog!D:D,A11,Backlog!I:I)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D12" s="2" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D12" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A12)</f>
         <v>2</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="3" t="n">
         <f aca="false">SUMIF(Backlog!D:D,A12,Backlog!I:I)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C13" s="2" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="B13" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D13" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A13)</f>
         <v>1</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="3" t="n">
         <f aca="false">SUMIF(Backlog!D:D,A13,Backlog!I:I)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D14" s="2" t="n">
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D14" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A14)</f>
         <v>2</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="3" t="n">
         <f aca="false">SUMIF(Backlog!D:D,A14,Backlog!I:I)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D15" s="2" t="n">
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D15" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A15)</f>
         <v>2</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="3" t="n">
         <f aca="false">SUMIF(Backlog!D:D,A15,Backlog!I:I)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D16" s="2" t="n">
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D16" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A16)</f>
-        <v>2</v>
-      </c>
-      <c r="E16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="3" t="n">
         <f aca="false">SUMIF(Backlog!D:D,A16,Backlog!I:I)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="9" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="10" t="n">
         <f aca="false">SUM(D2:D16)</f>
-        <v>33</v>
-      </c>
-      <c r="E17" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="E17" s="10" t="n">
         <f aca="false">SUM(E2:E16)</f>
         <v>0</v>
       </c>
@@ -2774,128 +2972,128 @@
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="1" width="15"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="F1" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!B:B,A2)</f>
-        <v>20</v>
-      </c>
-      <c r="C2" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <f aca="false">SUMIF(Backlog!B:B,A2,Backlog!I:I)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <f aca="false">COUNTIFS(Backlog!B:B,A2,Backlog!H:H,"Must")</f>
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <f aca="false">COUNTIFS(Backlog!B:B,A2,Backlog!H:H,"Should")</f>
-        <v>5</v>
-      </c>
-      <c r="F2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <f aca="false">COUNTIFS(Backlog!B:B,A2,Backlog!H:H,"Could")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="2" t="n">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!B:B,A3)</f>
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="3" t="n">
         <f aca="false">SUMIF(Backlog!B:B,A3,Backlog!I:I)</f>
         <v>0</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <f aca="false">COUNTIFS(Backlog!B:B,A3,Backlog!H:H,"Must")</f>
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <f aca="false">COUNTIFS(Backlog!B:B,A3,Backlog!H:H,"Should")</f>
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <f aca="false">COUNTIFS(Backlog!B:B,A3,Backlog!H:H,"Could")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="B4" s="2" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!B:B,A4)</f>
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <f aca="false">SUMIF(Backlog!B:B,A4,Backlog!I:I)</f>
         <v>0</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <f aca="false">COUNTIFS(Backlog!B:B,A4,Backlog!H:H,"Must")</f>
         <v>2</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <f aca="false">COUNTIFS(Backlog!B:B,A4,Backlog!H:H,"Should")</f>
         <v>2</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="3" t="n">
         <f aca="false">COUNTIFS(Backlog!B:B,A4,Backlog!H:H,"Could")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="B5" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="B5" s="10" t="n">
         <f aca="false">SUM(B2:B4)</f>
-        <v>33</v>
-      </c>
-      <c r="C5" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="C5" s="10" t="n">
         <f aca="false">SUM(C2:C4)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="10" t="n">
         <f aca="false">SUM(D2:D4)</f>
         <v>17</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="10" t="n">
         <f aca="false">SUM(E2:E4)</f>
-        <v>10</v>
-      </c>
-      <c r="F5" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="F5" s="10" t="n">
         <f aca="false">SUM(F2:F4)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Solvix-Full-Story-Backlog.xlsx
+++ b/docs/Solvix-Full-Story-Backlog.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Phase Overview" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Backlog!$A$1:$K$38</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Backlog!$A$1:$K$41</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="250">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -171,273 +171,273 @@
     <t xml:space="preserve">epic:requirement-understanding, priority:should, type:feature, phase:1</t>
   </si>
   <si>
+    <t xml:space="preserve">SLX-B3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produce a reviewable task plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a tech lead, I want the agent to break a larger requirement into a task plan I can review before it starts editing, so that I can catch scope issues early.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent outputs an ordered plan (files to touch, approach) before any code is modified, and waits for approval if the task is flagged as large/risky.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-C1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C: Code Modification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate diffs, not full-file rewrites</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want the agent to generate a code diff (not full-file rewrites), so that changes are minimal and reviewable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Output is a unified diff/patch, not a full file replacement, except when creating new files.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epic:code-modification, priority:must, type:feature, phase:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-C2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write/update tests alongside changes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want the agent to write or update tests alongside code changes, so that the change is verifiable and future-proof.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For any behavior change, at least one corresponding test is added or updated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epic:code-modification, priority:should, type:feature, phase:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run test suite after edits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want the agent to run the existing test suite after making changes, so that regressions are caught immediately.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test suite runs automatically post-edit; results (pass/fail + output) are captured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-C4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retry and self-correct on failure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want the agent to retry and self-correct when tests fail, so that I don't have to manually debug its first attempt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On failure, error output is fed back to the reasoning engine, which proposes a revised diff, up to a configurable retry limit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D: Human Oversight &amp; Trust</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deliver changes as pull requests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a tech lead, I want every agent change delivered as a pull request, so that a human always reviews before merge.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No commits land on protected branches without PR + approval flow.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epic:human-oversight, priority:must, type:feature, phase:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-D2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show reasoning trace in PR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a reviewer, I want to see the agent's reasoning trace alongside the diff, so that I understand why it made each change.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR description includes a summary of the plan, key decisions, and test results.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epic:human-oversight, priority:should, type:feature, phase:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-D3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accept conversational PR feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want to reject or request changes to an agent's PR conversationally, so that I can course-correct without starting over.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feedback on a PR is fed back into the agent's context for a revised attempt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Could</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epic:human-oversight, priority:could, type:feature, phase:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-D4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task outcomes dashboard (basic/CLI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As an engineering manager, I want visibility into how many tasks the agent attempted, resolved, or failed, so that I can gauge its reliability over time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A dashboard/log shows task outcomes, retry counts, and time-to-resolution.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epic:human-oversight, priority:could, type:chore, phase:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E: Safety &amp; Guardrails</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandbox all code execution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want the agent to run in a sandboxed environment, so that it can't affect my machine or production systems directly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All code execution happens in an isolated container/VM with no access to host secrets or unrelated systems.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epic:safety, priority:must, type:chore, phase:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-E2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm before destructive operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want the agent to ask for explicit confirmation before destructive operations, so that mistakes are never silent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any operation on a configurable 'dangerous ops' list requires an explicit user confirmation step.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epic:safety, priority:must, type:feature, phase:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-E3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cap retries per task</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want a hard cap on retries per task, so that a stuck task doesn't burn unbounded time or API cost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configurable max retry count; task is marked 'needs human help' once exceeded, rather than looping forever.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-F1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F: Developer Experience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submit tasks via CLI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want to submit a task via CLI, so that I can integrate this into my existing terminal workflow.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`solvix run "&lt;task description&gt;"` triggers the full loop against the current repo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epic:dev-experience, priority:must, type:feature, phase:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-F2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live progress updates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want to see live progress (what file it's looking at, what it's trying), so that I'm not staring at a black box.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming status updates during retrieval, planning, editing, and testing phases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epic:dev-experience, priority:should, type:feature, phase:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-F3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configurable path allow/deny list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want to configure which parts of the repo the agent is allowed to touch, so that sensitive files are never modified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A config file (.solvix.yml) supports include/exclude paths, enforced before any write operation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-P2-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 2: Trust &amp; UX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G: Platform Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GitHub App integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want the agent to run as a GitHub App that responds to issues/PR comments, so that I don't need the CLI to trigger tasks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installing the GitHub App on a repo allows triggering tasks via issue labels or comments; agent posts PRs automatically without local CLI use.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epic:platform-integration, priority:must, type:feature, phase:2</t>
+  </si>
+  <si>
     <t xml:space="preserve">To Do</t>
   </si>
   <si>
-    <t xml:space="preserve">SLX-B3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produce a reviewable task plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a tech lead, I want the agent to break a larger requirement into a task plan I can review before it starts editing, so that I can catch scope issues early.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent outputs an ordered plan (files to touch, approach) before any code is modified, and waits for approval if the task is flagged as large/risky.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLX-C1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C: Code Modification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate diffs, not full-file rewrites</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a developer, I want the agent to generate a code diff (not full-file rewrites), so that changes are minimal and reviewable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Output is a unified diff/patch, not a full file replacement, except when creating new files.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epic:code-modification, priority:must, type:feature, phase:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLX-C2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Write/update tests alongside changes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a developer, I want the agent to write or update tests alongside code changes, so that the change is verifiable and future-proof.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For any behavior change, at least one corresponding test is added or updated.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epic:code-modification, priority:should, type:feature, phase:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLX-C3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Run test suite after edits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a developer, I want the agent to run the existing test suite after making changes, so that regressions are caught immediately.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test suite runs automatically post-edit; results (pass/fail + output) are captured.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLX-C4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retry and self-correct on failure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a developer, I want the agent to retry and self-correct when tests fail, so that I don't have to manually debug its first attempt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On failure, error output is fed back to the reasoning engine, which proposes a revised diff, up to a configurable retry limit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLX-D1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D: Human Oversight &amp; Trust</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deliver changes as pull requests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a tech lead, I want every agent change delivered as a pull request, so that a human always reviews before merge.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No commits land on protected branches without PR + approval flow.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epic:human-oversight, priority:must, type:feature, phase:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLX-D2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Show reasoning trace in PR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a reviewer, I want to see the agent's reasoning trace alongside the diff, so that I understand why it made each change.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PR description includes a summary of the plan, key decisions, and test results.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epic:human-oversight, priority:should, type:feature, phase:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLX-D3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accept conversational PR feedback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a developer, I want to reject or request changes to an agent's PR conversationally, so that I can course-correct without starting over.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feedback on a PR is fed back into the agent's context for a revised attempt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Could</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epic:human-oversight, priority:could, type:feature, phase:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLX-D4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task outcomes dashboard (basic/CLI)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As an engineering manager, I want visibility into how many tasks the agent attempted, resolved, or failed, so that I can gauge its reliability over time.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A dashboard/log shows task outcomes, retry counts, and time-to-resolution.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epic:human-oversight, priority:could, type:chore, phase:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLX-E1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E: Safety &amp; Guardrails</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandbox all code execution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a developer, I want the agent to run in a sandboxed environment, so that it can't affect my machine or production systems directly.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All code execution happens in an isolated container/VM with no access to host secrets or unrelated systems.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epic:safety, priority:must, type:chore, phase:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLX-E2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm before destructive operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a developer, I want the agent to ask for explicit confirmation before destructive operations, so that mistakes are never silent.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any operation on a configurable 'dangerous ops' list requires an explicit user confirmation step.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epic:safety, priority:must, type:feature, phase:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLX-E3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cap retries per task</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a developer, I want a hard cap on retries per task, so that a stuck task doesn't burn unbounded time or API cost.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Configurable max retry count; task is marked 'needs human help' once exceeded, rather than looping forever.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLX-F1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F: Developer Experience</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submit tasks via CLI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a developer, I want to submit a task via CLI, so that I can integrate this into my existing terminal workflow.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`solvix run "&lt;task description&gt;"` triggers the full loop against the current repo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epic:dev-experience, priority:must, type:feature, phase:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLX-F2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live progress updates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a developer, I want to see live progress (what file it's looking at, what it's trying), so that I'm not staring at a black box.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming status updates during retrieval, planning, editing, and testing phases.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epic:dev-experience, priority:should, type:feature, phase:1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLX-F3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Configurable path allow/deny list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a developer, I want to configure which parts of the repo the agent is allowed to touch, so that sensitive files are never modified.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A config file (.solvix.yml) supports include/exclude paths, enforced before any write operation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLX-P2-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 2: Trust &amp; UX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G: Platform Integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint 9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GitHub App integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a developer, I want the agent to run as a GitHub App that responds to issues/PR comments, so that I don't need the CLI to trigger tasks.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Installing the GitHub App on a repo allows triggering tasks via issue labels or comments; agent posts PRs automatically without local CLI use.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epic:platform-integration, priority:must, type:feature, phase:2</t>
-  </si>
-  <si>
     <t xml:space="preserve">SLX-P2-2</t>
   </si>
   <si>
@@ -681,7 +681,46 @@
     <t xml:space="preserve">As a developer, I want an interactive mode where the agent proposes one diff at a time directly against my real working files (not a sandboxed scratch copy ending in a PR), so that I can review and approve changes live, similar to working with a pair-programming assistant.</t>
   </si>
   <si>
-    <t xml:space="preserve">Running  reads the repo the same way as , but proposes each diff directly against the real working tree one step at a time, waits for explicit per-diff approval before writing it, and does not require a full task to complete before any change is visible — this is an additive mode alongside the existing sandboxed, PR-based  flow, not a replacement for it.</t>
+    <t xml:space="preserve">Running solvix chat reads the repo the same way as solvix run, but proposes each diff directly against the real working tree one step at a time, waits for explicit per-diff approval before writing it, and does not require a full task to complete before any change is visible — this is an additive mode alongside the existing sandboxed, PR-based solvix run flow, not a replacement for it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-C5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detect assertion-gaming on retry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want the system to flag (not just silently accept) a retry that passes tests by rewriting an expected/literal value in a test assertion rather than fixing the implementation, so that a locally-run smaller model cannot satisfy "tests pass" by rewriting the test to match whatever the code already does.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Given a retry attempt whose diff modifies a literal/expected value inside an existing or newly-added assertion (e.g. a hardcoded number, string, or comparison target) in the same step where the previous attempt failed specifically because of that literal, the step result flags this explicitly (e.g. assertion_literal_changed=True with the before/after values) even if the test suite ultimately passes — verified with a case reproducing the real add(0.1, 0.2) == 0.3 -&gt; == 0.30000000000000004 example found during SLX-D2's smoke test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epic:code-modification, priority:should, type:bug, phase:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-C6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feed diff-generation failures into the outer retry loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want a DiffGenerationError (raised after propose_diff exhausts its own internal one-shot correction retry) to consume one attempt of the outer per-step retry budget rather than immediately terminating the step with needs_human_help=True, so that a malformed/unparseable diff gets the same real retry opportunity a failed test already gets, instead of wasting unused attempts and forcing a manual full re-run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Given a step whose first propose_diff call raises DiffGenerationError, execute_step_with_verification treats this as a normal retriable failure within its own outer per-step budget (max_retries) — feeding the parse/diff-generation failure reason into the next attempt's prompt, the same way a test failure's output is fed back today — and only sets needs_human_help=True once the OUTER budget itself is exhausted, not on the first DiffGenerationError. Reproduced by the real missing ---/+++ header case found live during SLX-F2's smoke test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-C7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detect tolerance/rounding-wrapper assertion-gaming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want the system to also flag a retry that makes a failing assertion pass by wrapping the comparison in a tolerance/rounding mechanism (round(), pytest.approx, abs(x-y)&lt;epsilon, or similar) rather than fixing the implementation, so that this style of gaming — found during SLX-C5's smoke test to be this model's more common default cheating behavior, more common than the literal-value swap SLX-C5 already catches — does not silently pass undetected.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Given a retry attempt whose diff introduces a tolerance/rounding wrapper (round(), pytest.approx, math.isclose, or an inline absolute-difference-under-epsilon pattern) around a comparison in the same assertion where the previous attempt failed on an exact-equality check, the step result flags this explicitly (with the before/after assertion text), even if the test suite ultimately passes — reusing SLX-C5's existing assertion_gaming_suspected/assertion_gaming_details fields and "Needs attention" PR surfacing rather than inventing a new mechanism.</t>
   </si>
   <si>
     <t xml:space="preserve">Focus</t>
@@ -1263,7 +1302,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
@@ -1485,12 +1524,12 @@
         <v>47</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>12</v>
@@ -1502,13 +1541,13 @@
         <v>23</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>18</v>
@@ -1525,25 +1564,25 @@
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>18</v>
@@ -1552,7 +1591,7 @@
         <v>19</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>21</v>
@@ -1560,25 +1599,25 @@
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>32</v>
@@ -1587,33 +1626,33 @@
         <v>19</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>18</v>
@@ -1622,7 +1661,7 @@
         <v>33</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>21</v>
@@ -1630,25 +1669,25 @@
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>18</v>
@@ -1657,7 +1696,7 @@
         <v>19</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>21</v>
@@ -1665,25 +1704,25 @@
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>18</v>
@@ -1692,33 +1731,33 @@
         <v>33</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>32</v>
@@ -1727,103 +1766,103 @@
         <v>33</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="7" t="s">
         <v>89</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>90</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="H15" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>33</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>18</v>
@@ -1832,7 +1871,7 @@
         <v>19</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>21</v>
@@ -1840,25 +1879,25 @@
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>18</v>
@@ -1867,7 +1906,7 @@
         <v>33</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>21</v>
@@ -1875,25 +1914,25 @@
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>18</v>
@@ -1902,7 +1941,7 @@
         <v>40</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>21</v>
@@ -1910,25 +1949,25 @@
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>18</v>
@@ -1937,7 +1976,7 @@
         <v>40</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>21</v>
@@ -1945,25 +1984,25 @@
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>32</v>
@@ -1972,33 +2011,33 @@
         <v>33</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E21" s="3" t="s">
+      <c r="F21" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>18</v>
@@ -2007,7 +2046,7 @@
         <v>40</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>21</v>
@@ -2015,37 +2054,37 @@
     </row>
     <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="C22" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I22" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2053,13 +2092,13 @@
         <v>137</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>138</v>
@@ -2080,7 +2119,7 @@
         <v>141</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2088,10 +2127,10 @@
         <v>142</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>143</v>
@@ -2109,13 +2148,13 @@
         <v>18</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>147</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2123,7 +2162,7 @@
         <v>148</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>13</v>
@@ -2150,7 +2189,7 @@
         <v>152</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2158,10 +2197,10 @@
         <v>153</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>154</v>
@@ -2176,7 +2215,7 @@
         <v>157</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>19</v>
@@ -2185,7 +2224,7 @@
         <v>158</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2193,10 +2232,10 @@
         <v>159</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>154</v>
@@ -2211,7 +2250,7 @@
         <v>162</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>33</v>
@@ -2220,7 +2259,7 @@
         <v>163</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2228,10 +2267,10 @@
         <v>164</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>165</v>
@@ -2249,13 +2288,13 @@
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>141</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2284,13 +2323,13 @@
         <v>18</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>176</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2325,7 +2364,7 @@
         <v>176</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2351,16 +2390,16 @@
         <v>185</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>186</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2389,13 +2428,13 @@
         <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>191</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2421,7 +2460,7 @@
         <v>196</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>19</v>
@@ -2430,7 +2469,7 @@
         <v>186</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2441,7 +2480,7 @@
         <v>170</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>193</v>
@@ -2465,7 +2504,7 @@
         <v>201</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2500,7 +2539,7 @@
         <v>34</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2535,7 +2574,7 @@
         <v>34</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2546,10 +2585,10 @@
         <v>12</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>211</v>
@@ -2570,10 +2609,10 @@
         <v>214</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>215</v>
       </c>
@@ -2596,20 +2635,125 @@
         <v>218</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>186</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>48</v>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K38"/>
+  <autoFilter ref="A1:K41"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2644,13 +2788,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2661,7 +2805,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="D2" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A2)</f>
@@ -2680,7 +2824,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="D3" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A3)</f>
@@ -2699,7 +2843,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="D4" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A4)</f>
@@ -2712,13 +2856,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="D5" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A5)</f>
@@ -2731,13 +2875,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="D6" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A6)</f>
@@ -2750,13 +2894,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="D7" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A7)</f>
@@ -2769,17 +2913,17 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="D8" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A8)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E8" s="3" t="n">
         <f aca="false">SUMIF(Backlog!D:D,A8,Backlog!I:I)</f>
@@ -2794,7 +2938,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="D9" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A9)</f>
@@ -2807,13 +2951,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="D10" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A10)</f>
@@ -2829,10 +2973,10 @@
         <v>143</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="D11" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A11)</f>
@@ -2848,10 +2992,10 @@
         <v>154</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="D12" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A12)</f>
@@ -2867,7 +3011,7 @@
         <v>165</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>166</v>
@@ -2889,7 +3033,7 @@
         <v>170</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="D14" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A14)</f>
@@ -2908,7 +3052,7 @@
         <v>170</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="D15" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A15)</f>
@@ -2927,7 +3071,7 @@
         <v>170</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="D16" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A16)</f>
@@ -2940,13 +3084,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="10" t="n">
         <f aca="false">SUM(D2:D16)</f>
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E17" s="10" t="n">
         <f aca="false">SUM(E2:E16)</f>
@@ -2981,10 +3125,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>18</v>
@@ -2993,7 +3137,7 @@
         <v>32</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3002,7 +3146,7 @@
       </c>
       <c r="B2" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!B:B,A2)</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="n">
         <f aca="false">SUMIF(Backlog!B:B,A2,Backlog!I:I)</f>
@@ -3014,7 +3158,7 @@
       </c>
       <c r="E2" s="3" t="n">
         <f aca="false">COUNTIFS(Backlog!B:B,A2,Backlog!H:H,"Should")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F2" s="3" t="n">
         <f aca="false">COUNTIFS(Backlog!B:B,A2,Backlog!H:H,"Could")</f>
@@ -3023,7 +3167,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B3" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!B:B,A3)</f>
@@ -3073,11 +3217,11 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B5" s="10" t="n">
         <f aca="false">SUM(B2:B4)</f>
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">SUM(C2:C4)</f>
@@ -3089,7 +3233,7 @@
       </c>
       <c r="E5" s="10" t="n">
         <f aca="false">SUM(E2:E4)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F5" s="10" t="n">
         <f aca="false">SUM(F2:F4)</f>

--- a/docs/Solvix-Full-Story-Backlog.xlsx
+++ b/docs/Solvix-Full-Story-Backlog.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Phase Overview" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Backlog!$A$1:$K$41</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Backlog!$A$1:$K$45</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="270">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -721,6 +721,66 @@
   </si>
   <si>
     <t xml:space="preserve">Given a retry attempt whose diff introduces a tolerance/rounding wrapper (round(), pytest.approx, math.isclose, or an inline absolute-difference-under-epsilon pattern) around a comparison in the same assertion where the previous attempt failed on an exact-equality check, the step result flags this explicitly (with the before/after assertion text), even if the test suite ultimately passes — reusing SLX-C5's existing assertion_gaming_suspected/assertion_gaming_details fields and "Needs attention" PR surfacing rather than inventing a new mechanism.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-A6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 1 (retro)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handle non-UTF-8 files without crashing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want indexing and import-graph analysis to skip or gracefully handle files that are not valid UTF-8, so that running Solvix against a real repo does not hard-crash the entire tool the first time it encounters one non-UTF-8 file.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Given a repo containing at least one .py file with invalid UTF-8 byte sequences, index_repo() and build_import_graph() complete successfully (skipping or safely decoding the offending file with a clear warning) rather than raising an uncaught UnicodeDecodeError that terminates the whole solvix run/revise command. Reproduced live on the real Solvix repo itself (2026-07-05).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epic:repo-understanding, priority:must, type:bug, phase:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-E5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint (retro)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandbox missing Solvix's own dependencies when self-hosting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer running Solvix on the Solvix repo itself (or any repo whose test suite depends on packages the generic sandbox image does not have, like yaml/tree_sitter_python), I want the sandbox to have the actual project's dependencies installed, so that test collection does not fail purely due to missing packages unrelated to the actual code change being verified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Given a target repo with a requirements.txt/pyproject.toml declaring dependencies not present in the sandbox's base image, run_tests_on_diff installs those dependencies into the sandbox (or the sandbox image is built from the repo's own environment where available) before running the test command, so that a step does not fail verification purely due to missing unrelated packages. Reproduced live running solvix on its own repo (2026-07-05).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-C8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sanitize internal paths from model-facing retry feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want retry/correction prompts fed back to the model to reference the real target file (e.g. cli.py) rather than raw internal scratch/temp-file paths from patch/git error output, so that the model is not confused into thinking it is missing a real file it actually already has full content for.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Given a diff-apply or patch failure whose raw error output contains an internal scratch-directory path (e.g. /tmp/.../target), the correction prompt fed back to propose_diff replaces or strips that internal path in favor of the actual target file name, and does not cause the model to request "the content of file X" for a file that is actually just Solvix's own temp-file naming. Reproduced live: a real --version-flag task's attempt 3 refused to produce a diff, explicitly asking for the content of a file called "target" — which is only the internal scratch path, not a real missing file.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-F4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graceful check for Ollama availability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want a clean, actionable error message if Ollama is not running when I invoke solvix run/revise, so that I get the same friendly precondition-failure experience Docker already provides (SLX-E1), instead of a raw unhandled ConnectionError traceback.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Given Ollama is not reachable at its configured endpoint when solvix run/revise starts, the CLI fails fast with a clear message (e.g. "Error: Ollama is not available. Start it with ollama serve before running Solvix.") before attempting any LLM call, mirroring ensure_docker_available()'s pattern -- no raw traceback reaches the user. Reproduced live: a real run crashed with an unhandled requests.exceptions.ConnectionError from deep inside check_ambiguity/llm_client.complete when Ollama was not running.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epic:dev-experience, priority:must, type:bug, phase:1</t>
   </si>
   <si>
     <t xml:space="preserve">Focus</t>
@@ -1302,7 +1362,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
@@ -2752,8 +2812,148 @@
         <v>136</v>
       </c>
     </row>
+    <row r="42" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K41"/>
+  <autoFilter ref="A1:K45"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2788,13 +2988,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2805,7 +3005,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="D2" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A2)</f>
@@ -2824,7 +3024,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="D3" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A3)</f>
@@ -2843,7 +3043,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="D4" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A4)</f>
@@ -2862,7 +3062,7 @@
         <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="D5" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A5)</f>
@@ -2881,7 +3081,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="D6" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A6)</f>
@@ -2900,7 +3100,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="D7" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A7)</f>
@@ -2919,7 +3119,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="D8" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A8)</f>
@@ -2938,7 +3138,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="D9" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A9)</f>
@@ -2957,7 +3157,7 @@
         <v>128</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="D10" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A10)</f>
@@ -2976,7 +3176,7 @@
         <v>128</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="D11" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A11)</f>
@@ -2995,7 +3195,7 @@
         <v>128</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="D12" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A12)</f>
@@ -3033,7 +3233,7 @@
         <v>170</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="D14" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A14)</f>
@@ -3052,7 +3252,7 @@
         <v>170</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="D15" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A15)</f>
@@ -3071,7 +3271,7 @@
         <v>170</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="D16" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A16)</f>
@@ -3084,7 +3284,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -3125,10 +3325,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>18</v>
@@ -3146,7 +3346,7 @@
       </c>
       <c r="B2" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!B:B,A2)</f>
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="n">
         <f aca="false">SUMIF(Backlog!B:B,A2,Backlog!I:I)</f>
@@ -3154,11 +3354,11 @@
       </c>
       <c r="D2" s="3" t="n">
         <f aca="false">COUNTIFS(Backlog!B:B,A2,Backlog!H:H,"Must")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" s="3" t="n">
         <f aca="false">COUNTIFS(Backlog!B:B,A2,Backlog!H:H,"Should")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2" s="3" t="n">
         <f aca="false">COUNTIFS(Backlog!B:B,A2,Backlog!H:H,"Could")</f>
@@ -3217,11 +3417,11 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="B5" s="10" t="n">
         <f aca="false">SUM(B2:B4)</f>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">SUM(C2:C4)</f>
@@ -3229,11 +3429,11 @@
       </c>
       <c r="D5" s="10" t="n">
         <f aca="false">SUM(D2:D4)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E5" s="10" t="n">
         <f aca="false">SUM(E2:E4)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5" s="10" t="n">
         <f aca="false">SUM(F2:F4)</f>

--- a/docs/Solvix-Full-Story-Backlog.xlsx
+++ b/docs/Solvix-Full-Story-Backlog.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Phase Overview" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Backlog!$A$1:$K$45</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Backlog!$A$1:$K$46</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="275">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -781,6 +781,21 @@
   </si>
   <si>
     <t xml:space="preserve">epic:dev-experience, priority:must, type:bug, phase:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLX-C9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fix unhandled crash on missing-parent-directory diff apply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a developer, I want a diff-apply failure caused by a missing parent directory (e.g. a mis-detected new-file diff, or a plan targeting a path that does not exist in this repo) to degrade cleanly to needs_human_help like every other failure mode, so that a wrong file path can never cause a raw unhandled crash instead of a clean, reported failure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Given a diff whose target path's parent directory does not exist on disk, and whose is_new_file detection is wrong (e.g. because the diff header does not follow the /dev/null convention the heuristic relies on), execution/test_runner.py's apply_diff either (a) creates the missing parent directory regardless of is_new_file, or (b) fails with a caught, typed exception rather than an uncaught subprocess.CalledProcessError. execute_step_with_verification/run_task catch this failure the same way DiffGenerationError is already handled, surfacing a normal needs_human_help StepResult/TaskResult -- no raw traceback, no "unhandled error" reaching cli.py's outermost catch-all. Reproduced live (2026-07-05): a plan targeting a nonexistent root-level utils/strings.py path (real file lives at sample_repo/utils/strings.py) caused patch to exit 2 on a missing parent directory, raising an uncaught CalledProcessError.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epic:code-modification, priority:must, type:bug, phase:1</t>
   </si>
   <si>
     <t xml:space="preserve">Focus</t>
@@ -1362,7 +1377,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
@@ -2869,8 +2884,8 @@
       <c r="G43" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="H43" s="6" t="s">
-        <v>32</v>
+      <c r="H43" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>19</v>
@@ -2879,7 +2894,7 @@
         <v>214</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2949,11 +2964,46 @@
         <v>251</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>136</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K45"/>
+  <autoFilter ref="A1:K46"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2988,13 +3038,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3005,7 +3055,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D2" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A2)</f>
@@ -3024,7 +3074,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D3" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A3)</f>
@@ -3043,7 +3093,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D4" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A4)</f>
@@ -3062,7 +3112,7 @@
         <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="D5" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A5)</f>
@@ -3081,7 +3131,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D6" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A6)</f>
@@ -3100,7 +3150,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D7" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A7)</f>
@@ -3119,7 +3169,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D8" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A8)</f>
@@ -3138,7 +3188,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D9" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A9)</f>
@@ -3157,7 +3207,7 @@
         <v>128</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D10" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A10)</f>
@@ -3176,7 +3226,7 @@
         <v>128</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D11" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A11)</f>
@@ -3195,7 +3245,7 @@
         <v>128</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D12" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A12)</f>
@@ -3233,7 +3283,7 @@
         <v>170</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D14" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A14)</f>
@@ -3252,7 +3302,7 @@
         <v>170</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D15" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A15)</f>
@@ -3271,7 +3321,7 @@
         <v>170</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="D16" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!D:D,A16)</f>
@@ -3284,7 +3334,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -3325,10 +3375,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>18</v>
@@ -3346,7 +3396,7 @@
       </c>
       <c r="B2" s="3" t="n">
         <f aca="false">COUNTIF(Backlog!B:B,A2)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="n">
         <f aca="false">SUMIF(Backlog!B:B,A2,Backlog!I:I)</f>
@@ -3354,11 +3404,11 @@
       </c>
       <c r="D2" s="3" t="n">
         <f aca="false">COUNTIFS(Backlog!B:B,A2,Backlog!H:H,"Must")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" s="3" t="n">
         <f aca="false">COUNTIFS(Backlog!B:B,A2,Backlog!H:H,"Should")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" s="3" t="n">
         <f aca="false">COUNTIFS(Backlog!B:B,A2,Backlog!H:H,"Could")</f>
@@ -3417,11 +3467,11 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B5" s="10" t="n">
         <f aca="false">SUM(B2:B4)</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">SUM(C2:C4)</f>
@@ -3429,11 +3479,11 @@
       </c>
       <c r="D5" s="10" t="n">
         <f aca="false">SUM(D2:D4)</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E5" s="10" t="n">
         <f aca="false">SUM(E2:E4)</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" s="10" t="n">
         <f aca="false">SUM(F2:F4)</f>
